--- a/InputData/indst/_cement/CPSW/Cement Pathway Shareweight.xlsx
+++ b/InputData/indst/_cement/CPSW/Cement Pathway Shareweight.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CPSW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E0C555-8112-4CAD-8050-D4EF832FAF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2285B210-92B6-4543-B0E6-99680946BA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>CPSW Cement Pathway Shareweight</t>
   </si>
@@ -44,21 +44,6 @@
     <t>Sources:</t>
   </si>
   <si>
-    <t>U.S. Department of Energy, Office of Clean Energy Demonstrations (OCED)</t>
-  </si>
-  <si>
-    <t>https://www.energy.gov/oced/oced-cement-and-concrete-industrial-demonstrations</t>
-  </si>
-  <si>
-    <t>https://www.heidelbergmaterials.com/en/pr-30-06-2025</t>
-  </si>
-  <si>
-    <t>Heidelberg Materials; Coolbrook; Adani</t>
-  </si>
-  <si>
-    <t>https://www.heidelbergmaterials.com/en/pr-06-02-2025</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
@@ -74,9 +59,6 @@
     <t>dry kiln with precalciner</t>
   </si>
   <si>
-    <t>Incumbent - always eligible; set to the first model year so the gate is trivially true every year.</t>
-  </si>
-  <si>
     <t>dry kiln with CCS</t>
   </si>
   <si>
@@ -86,68 +68,135 @@
     <t>alternative chemistry cement</t>
   </si>
   <si>
-    <t>Gate formula: =IF(year&gt;=gate year, 1, 0), one cell per pathway-year</t>
-  </si>
-  <si>
-    <t>Why the CCS and alternative-chemistry gates are late</t>
-  </si>
-  <si>
-    <t>OCED Cement and Concrete Industrial Demonstrations</t>
-  </si>
-  <si>
-    <t>DOE cancelled its demonstration awards to Heidelberg Materials' Mitchell, Indiana CCS project ($500 million), Brimstone ($189 million), and Sublime Systems ($87 million) in May 2025. We read this as meaning no U.S. project for these technologies has a funded path to commercial operation soon, which pushes the gate years for dry kiln with CCS (2030) and alternative chemistry cement (2033) later. The gate years themselves are our judgment, not dates taken from the announcements. Sublime's Holyoke plant is a demonstration of about 30 thousand metric tons per year, far below commercial scale.</t>
-  </si>
-  <si>
     <t>Evidence that cement CCS works at scale</t>
   </si>
   <si>
     <t>Heidelberg Materials</t>
   </si>
   <si>
-    <t>Brevik CCS plant start-up announcement (Norway, Longship / Northern Lights project)</t>
-  </si>
-  <si>
-    <t>The Brevik plant began capturing CO2 at commercial scale in June 2025. It shows cement CCS is technically viable abroad and keeps our gate for dry kiln with CCS from moving later still. It is not a U.S. project.</t>
-  </si>
-  <si>
     <t>Electric kiln status</t>
   </si>
   <si>
-    <t>ELECTRA plasma-kiln first test announcement (February 2025), plus Coolbrook and Adani development-stage project announcements</t>
-  </si>
-  <si>
-    <t>Electric and plasma-heated kiln technology is still at pilot or development stage, with no commercial-scale project announced. The 2035 gate year for electric kiln is our judgment, not a commissioning date. The link covers the ELECTRA test.</t>
-  </si>
-  <si>
     <t>Purpose and layout</t>
   </si>
   <si>
-    <t>This file tells the EPS cement module when each kiln pathway becomes available to be chosen for new kilns and for overhaul-or-replace decisions. A value of 0 in a year means the pathway cannot be chosen that year; 1 means it can. Among the pathways that are available, the model picks by comparing costs (see the CPCC, CRSW, and related files), so this file only opens or closes the door.
-The 'Gate Parameters' tab holds one gate year per pathway and is the place to change a value: it is the only tab with judgment inputs. The 'Calc' tab sets each pathway-year to 1 once the year reaches the gate year and 0 before, and the 'CPSW' tab reads from 'Calc' and is what gets exported to CPSW.csv.</t>
-  </si>
-  <si>
     <t>U.S. values</t>
   </si>
   <si>
-    <t>The dry kiln with precalciner is today's standard technology and is available in every year. The first year each of the other pathways can be chosen is 2030 for dry kiln with CCS, 2033 for alternative chemistry cement, and 2035 for electric kiln. These gate years are our own judgment based on the project landscape described under Sources; none is a date reported by a developer or agency.</t>
-  </si>
-  <si>
-    <t>Limits</t>
-  </si>
-  <si>
-    <t>A step from 0 to 1 means a pathway is either fully available or not at all, so the file does not describe a gradual commercial ramp-up. How fast a newly available pathway is adopted depends on the model's cost comparison and capacity limits, not on this file. For a non-U.S. region, the gate years should be reviewed against that region's project pipeline.</t>
-  </si>
-  <si>
-    <t>May 2025 DOE/OCED cancellations (Heidelberg Mitchell CCS); Brevik proves the technology abroad but there is no live US commercial path. EI judgment.</t>
-  </si>
-  <si>
-    <t>Pilot-only (Heidelberg ELECTRA Feb 2025, Coolbrook/Adani). EI judgment.</t>
-  </si>
-  <si>
-    <t>May 2025 DOE/OCED cancellations (Brimstone, Sublime); Sublime Holyoke is a 30 kt/yr demonstration. EI judgment.</t>
-  </si>
-  <si>
     <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>Ramp length (years to reach full weight)</t>
+  </si>
+  <si>
+    <t>Incumbent - always eligible.</t>
+  </si>
+  <si>
+    <t>No US cement CCS investment decision as of Oct 2026; ~4-4.5 years decision-to-operation (Brevik, Padeswood) plus Class VI permitting. DOE Liftoff TRL 6-7.5; IEA guide: commercial pre-2030.</t>
+  </si>
+  <si>
+    <t>TRL 5-6 (DOE Liftoff; IEA guide). Heidelberg ELECTRA 300 kW test 2025, 1 MW unit 2026-27 vs ~170 MW per plant; Holcim/SaltX electric pilot targeted 2028.</t>
+  </si>
+  <si>
+    <t>TRL 3-5 for alternative production methods (DOE Liftoff); IEA guide: commercial 2035. Brimstone demo expected 2028; Sublime Holyoke paused Dec 2025.</t>
+  </si>
+  <si>
+    <t>Gate formula: 0 before the gate year, then rising in equal steps to 1 over the ramp length</t>
+  </si>
+  <si>
+    <t>Technology readiness of each pathway</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>Pathways to Commercial Liftoff: Low-Carbon Cement (updated February 2025)</t>
+  </si>
+  <si>
+    <t>https://liftoff.energy.gov/wp-content/uploads/2023/12/LIFTOFF_Cement_Updated-2.6.25.pdf</t>
+  </si>
+  <si>
+    <t>Readiness levels: carbon capture 6-7.5, with 3-5 U.S. demonstrations expected before 2030; kiln electrification 5-6 ('next horizon'); alternative production methods 3-5. We read the readiness table through DOE's March 2024 ITIAC briefing, because the Liftoff site did not load.</t>
+  </si>
+  <si>
+    <t>Expected commercial availability</t>
+  </si>
+  <si>
+    <t>World Economic Forum and Accenture, citing the IEA Clean Energy Technology Guide</t>
+  </si>
+  <si>
+    <t>Net-Zero Industry Tracker 2024: Cement</t>
+  </si>
+  <si>
+    <t>https://reports.weforum.org/docs/WEF_Net_Zero_Industry_Tracker_2024_Cement.pdf</t>
+  </si>
+  <si>
+    <t>Post-combustion capture commercially available before 2030 (readiness 7-8); kiln electrification around 2030 (readiness 5, covering electrification generally, not full electric clinkering); alternative binders and production methods around 2035.</t>
+  </si>
+  <si>
+    <t>Brevik CCS plant opening (Norway)</t>
+  </si>
+  <si>
+    <t>https://www.heidelbergmaterials.com/en/pr-2025-06-18</t>
+  </si>
+  <si>
+    <t>Brevik began capturing about 400,000 metric tons of CO2 a year in June 2025, and the Padeswood (UK) project reached its investment decision in September 2025, targeting 2029. Both took roughly 4-4.5 years from investment decision to operation.</t>
+  </si>
+  <si>
+    <t>U.S. CCS project status</t>
+  </si>
+  <si>
+    <t>Heidelberg Materials North America</t>
+  </si>
+  <si>
+    <t>Mitchell, Indiana CCS project update</t>
+  </si>
+  <si>
+    <t>https://www.heidelbergmaterials.us/home/news/news/2025/02/24/heidelberg-materials-north-america-announces-new-milestone-for-mitchell-ccs-project</t>
+  </si>
+  <si>
+    <t>As of October 2026 we found no investment decision on a U.S. cement CCS project; DOE cancelled its Mitchell demonstration award in May 2025, and Heidelberg's Edmonton project was put on hold in August 2026. Class VI CO2 storage permits take about two to three years.</t>
+  </si>
+  <si>
+    <t>Global Cement</t>
+  </si>
+  <si>
+    <t>Heating up cement kilns</t>
+  </si>
+  <si>
+    <t>https://globalcement.com/news/analysis/19853-heating-up-cement-kilns-september-2025</t>
+  </si>
+  <si>
+    <t>Heidelberg's ELECTRA plasma kiln ran a 300 kW test for 54 hours in 2025, with a 1 MW unit planned for 2026-27; a full plant needs roughly 170 MW. Holcim and SaltX are aiming for a European electric pilot plant by 2028 (reported second-hand).</t>
+  </si>
+  <si>
+    <t>Alternative chemistry status</t>
+  </si>
+  <si>
+    <t>The Reminder (Holyoke, MA)</t>
+  </si>
+  <si>
+    <t>Sublime Systems announces Holyoke project pause</t>
+  </si>
+  <si>
+    <t>https://thereminder.com/local-news/hampden-county/holyoke/sublime-systems-announces-holyoke-project-pause/</t>
+  </si>
+  <si>
+    <t>Sublime paused its Holyoke plant in December 2025 after losing its $87 million DOE award. Brimstone has not produced at commercial scale; its demonstration plant is expected in 2028 (MIT Technology Review, October 2026).</t>
+  </si>
+  <si>
+    <t>This file tells the EPS cement module when each kiln pathway becomes available to be chosen for new kilns and for overhaul-or-replace decisions. It multiplies each pathway's weight in the model's cost-based choice: 0 means the pathway cannot be chosen, 1 means it competes on cost alone, and values in between let a newly available pathway enter gradually.
+The 'Gate Parameters' tab holds a gate year and a ramp length for each pathway; these are the values to change. The 'Calc' tab sets each pathway-year to 0 before the gate year and then raises it in equal steps to 1 over the ramp length. The 'CPSW' tab reads from 'Calc' and is exported to CPSW.csv.</t>
+  </si>
+  <si>
+    <t>The dry kiln with precalciner is available in every year. Dry kiln with CCS opens in 2031 and reaches full weight in 2033 (three-year ramp). Alternative chemistry cement opens in 2034 and reaches full weight in 2037. The electric kiln opens in 2035 and reaches full weight in 2039.
+Because EPS adds capacity without a construction lag, the gate year is the first year a U.S. plant could plausibly be running: the first likely investment decision plus about four years to build (and, for CCS, the CO2 storage permit). The ramps reflect the time between the first plant and the technology being widely offered. The years are our judgment from the evidence under Sources; none is a date announced by a developer or agency.</t>
+  </si>
+  <si>
+    <t>What would move the dates</t>
+  </si>
+  <si>
+    <t>A U.S. cement CCS investment decision, or a faster Class VI permitting track, would pull the CCS gate earlier; the 45Q credit's construction-start deadline matters as well. A multi-megawatt electric kiln or calciner running at an existing plant would pull the electric kiln earlier; if the pathway is read as an electric calciner only, about 2032 would be defensible. Brimstone's 2028 demonstration and Sublime's restart are the signposts for alternative chemistry. For a non-U.S. region, review the gates against that region's project pipeline.</t>
   </si>
 </sst>
 </file>
@@ -220,7 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -232,10 +281,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,146 +591,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="110.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>2025</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="7">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="7">
+        <v>2025</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="5">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="116" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>51</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{02AD7F37-A36B-4E01-9DDA-C8074CAF4D99}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{BDD21DC4-09E2-4395-8136-F384AA248DF1}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{319A8284-F05D-47A1-A61A-A2BE5EC99625}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{D500685F-96EB-4E3D-9698-5004F35CA647}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{91688CC9-D65B-42E7-B6DC-C93D336E7FC1}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{4F94FEC0-6E81-490A-ABB3-43B9F5EC6F69}"/>
+    <hyperlink ref="D7" r:id="rId4" xr:uid="{F4F36724-2628-4632-BEB2-E3A1F81DB5EB}"/>
+    <hyperlink ref="D14" r:id="rId5" xr:uid="{706F1E53-C4B4-4C56-8BD7-0055307A8C40}"/>
+    <hyperlink ref="D21" r:id="rId6" xr:uid="{96745595-30C1-4723-A0D5-6DC42EC519CE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -688,67 +796,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>2021</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>2035</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -759,11 +883,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -856,503 +980,503 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <f>IF(B$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(B$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="C2">
-        <f>IF(C$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(C$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="D2">
-        <f>IF(D$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(D$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="E2">
-        <f>IF(E$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(E$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="F2">
-        <f>IF(F$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(F$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="G2">
-        <f>IF(G$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(G$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="H2">
-        <f>IF(H$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(H$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="I2">
-        <f>IF(I$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(I$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="J2">
-        <f>IF(J$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(J$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="K2">
-        <f>IF(K$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(K$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="L2">
-        <f>IF(L$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(L$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="M2">
-        <f>IF(M$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(M$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="N2">
-        <f>IF(N$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(N$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="O2">
-        <f>IF(O$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(O$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="P2">
-        <f>IF(P$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(P$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Q2">
-        <f>IF(Q$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Q$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="R2">
-        <f>IF(R$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(R$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="S2">
-        <f>IF(S$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(S$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="T2">
-        <f>IF(T$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(T$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="U2">
-        <f>IF(U$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(U$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="V2">
-        <f>IF(V$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(V$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="W2">
-        <f>IF(W$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(W$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="X2">
-        <f>IF(X$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(X$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Y2">
-        <f>IF(Y$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Y$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Z2">
-        <f>IF(Z$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Z$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AA2">
-        <f>IF(AA$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AA$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AB2">
-        <f>IF(AB$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AB$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AC2">
-        <f>IF(AC$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AC$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AD2">
-        <f>IF(AD$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AD$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AE2">
-        <f>IF(AE$1&gt;=VLOOKUP($A2,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <f>MIN(1,MAX(0,(AE$1-VLOOKUP($A2,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A2,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <f>IF(B$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(B$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="C3">
-        <f>IF(C$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(C$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f>IF(D$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(D$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f>IF(E$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(E$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>IF(F$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(F$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f>IF(G$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(G$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="H3">
-        <f>IF(H$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(H$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="I3">
-        <f>IF(I$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(I$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="J3">
-        <f>IF(J$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(J$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f>IF(K$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(K$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
       </c>
       <c r="L3">
-        <f>IF(L$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(L$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M3">
-        <f>IF(M$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(M$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N3">
-        <f>IF(N$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(N$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="O3">
-        <f>IF(O$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(O$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="P3">
-        <f>IF(P$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(P$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Q3">
-        <f>IF(Q$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Q$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="R3">
-        <f>IF(R$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(R$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="S3">
-        <f>IF(S$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(S$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="T3">
-        <f>IF(T$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(T$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="U3">
-        <f>IF(U$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(U$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="V3">
-        <f>IF(V$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(V$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="W3">
-        <f>IF(W$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(W$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="X3">
-        <f>IF(X$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(X$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Y3">
-        <f>IF(Y$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Y$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Z3">
-        <f>IF(Z$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Z$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AA3">
-        <f>IF(AA$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AA$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AB3">
-        <f>IF(AB$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AB$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AC3">
-        <f>IF(AC$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AC$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AD3">
-        <f>IF(AD$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AD$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AE3">
-        <f>IF(AE$1&gt;=VLOOKUP($A3,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+        <f>MIN(1,MAX(0,(AE$1-VLOOKUP($A3,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A3,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <f>IF(B$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(B$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f>IF(C$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(C$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f>IF(D$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(D$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>IF(E$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(E$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>IF(F$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(F$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>IF(G$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(G$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="H4">
-        <f>IF(H$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(H$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="I4">
-        <f>IF(I$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(I$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="J4">
-        <f>IF(J$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(J$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f>IF(K$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(K$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="L4">
-        <f>IF(L$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(L$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="M4">
-        <f>IF(M$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(M$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IF(N$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(N$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IF(O$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(O$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IF(P$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(P$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.2</v>
       </c>
       <c r="Q4">
-        <f>IF(Q$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(Q$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.4</v>
       </c>
       <c r="R4">
-        <f>IF(R$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(R$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.6</v>
       </c>
       <c r="S4">
-        <f>IF(S$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(S$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.8</v>
       </c>
       <c r="T4">
-        <f>IF(T$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(T$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="U4">
-        <f>IF(U$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(U$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="V4">
-        <f>IF(V$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(V$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="W4">
-        <f>IF(W$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(W$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="X4">
-        <f>IF(X$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(X$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Y4">
-        <f>IF(Y$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Y$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Z4">
-        <f>IF(Z$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Z$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AA4">
-        <f>IF(AA$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AA$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AB4">
-        <f>IF(AB$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AB$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AC4">
-        <f>IF(AC$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AC$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AD4">
-        <f>IF(AD$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AD$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AE4">
-        <f>IF(AE$1&gt;=VLOOKUP($A4,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+        <f>MIN(1,MAX(0,(AE$1-VLOOKUP($A4,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A4,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <f>IF(B$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(B$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="C5">
-        <f>IF(C$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(C$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="D5">
-        <f>IF(D$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(D$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>IF(E$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(E$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>IF(F$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(F$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>IF(G$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(G$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>IF(H$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(H$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="I5">
-        <f>IF(I$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(I$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="J5">
-        <f>IF(J$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(J$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="K5">
-        <f>IF(K$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(K$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="L5">
-        <f>IF(L$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(L$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="M5">
-        <f>IF(M$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(M$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IF(N$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(N$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
       </c>
       <c r="O5">
-        <f>IF(O$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(O$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.25</v>
       </c>
       <c r="P5">
-        <f>IF(P$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(P$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.5</v>
       </c>
       <c r="Q5">
-        <f>IF(Q$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
-        <v>1</v>
+        <f>MIN(1,MAX(0,(Q$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <f>IF(R$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(R$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="S5">
-        <f>IF(S$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(S$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="T5">
-        <f>IF(T$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(T$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="U5">
-        <f>IF(U$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(U$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="V5">
-        <f>IF(V$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(V$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="W5">
-        <f>IF(W$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(W$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="X5">
-        <f>IF(X$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(X$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Y5">
-        <f>IF(Y$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Y$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="Z5">
-        <f>IF(Z$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(Z$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AA5">
-        <f>IF(AA$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AA$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AB5">
-        <f>IF(AB$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AB$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AC5">
-        <f>IF(AC$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AC$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AD5">
-        <f>IF(AD$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AD$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
       <c r="AE5">
-        <f>IF(AE$1&gt;=VLOOKUP($A5,'Gate Parameters'!$A:$B,2,FALSE),1,0)</f>
+        <f>MIN(1,MAX(0,(AE$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
     </row>
@@ -1367,11 +1491,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -1464,9 +1588,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <f>Calc!B2</f>
@@ -1589,9 +1713,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <f>Calc!B3</f>
@@ -1631,15 +1755,15 @@
       </c>
       <c r="K3">
         <f>Calc!K3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <f>Calc!L3</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M3">
         <f>Calc!M3</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N3">
         <f>Calc!N3</f>
@@ -1714,9 +1838,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <f>Calc!B4</f>
@@ -1776,19 +1900,19 @@
       </c>
       <c r="P4">
         <f>Calc!P4</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Q4">
         <f>Calc!Q4</f>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="R4">
         <f>Calc!R4</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="S4">
         <f>Calc!S4</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T4">
         <f>Calc!T4</f>
@@ -1839,9 +1963,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <f>Calc!B5</f>
@@ -1893,19 +2017,19 @@
       </c>
       <c r="N5">
         <f>Calc!N5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <f>Calc!O5</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="P5">
         <f>Calc!P5</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q5">
         <f>Calc!Q5</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
         <f>Calc!R5</f>

--- a/InputData/indst/_cement/CPSW/Cement Pathway Shareweight.xlsx
+++ b/InputData/indst/_cement/CPSW/Cement Pathway Shareweight.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CPSW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2285B210-92B6-4543-B0E6-99680946BA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BB352A-0166-4877-9E31-4013B10368F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>CPSW Cement Pathway Shareweight</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>A U.S. cement CCS investment decision, or a faster Class VI permitting track, would pull the CCS gate earlier; the 45Q credit's construction-start deadline matters as well. A multi-megawatt electric kiln or calciner running at an existing plant would pull the electric kiln earlier; if the pathway is read as an electric calciner only, about 2032 would be defensible. Brimstone's 2028 demonstration and Sublime's restart are the signposts for alternative chemistry. For a non-U.S. region, review the gates against that region's project pipeline.</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>No electric kiln with integrated capture runs at industrial scale: Calix LEILAC-2 delayed with no timeline (June 2026), the ZETA electric calciner demo paused after pre-FEED, EU ELECTRA at pilot scale. Opens two years after the plain electric kiln and reaches full weight in 2042 (judgement; no source gives a commercial year).</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Opens in 2037 and reaches full weight in 2042 (Gate Parameters tab): two years after the plain electric kiln, because no electric kiln with integrated capture runs at industrial scale yet. Judgement, not a sourced date.</t>
   </si>
 </sst>
 </file>
@@ -269,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -287,6 +299,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -591,21 +609,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="110.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.6328125" customWidth="1"/>
-    <col min="4" max="4" width="110.6328125" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="110.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -616,7 +634,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
@@ -624,7 +642,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>24</v>
       </c>
@@ -632,7 +650,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2025</v>
       </c>
@@ -640,7 +658,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
@@ -648,7 +666,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>26</v>
       </c>
@@ -656,7 +674,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
@@ -664,7 +682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
@@ -672,7 +690,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
@@ -680,7 +698,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>2024</v>
       </c>
@@ -688,7 +706,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
@@ -696,7 +714,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>31</v>
       </c>
@@ -704,7 +722,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
@@ -712,7 +730,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
         <v>11</v>
       </c>
@@ -720,7 +738,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>32</v>
       </c>
@@ -728,7 +746,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7">
         <v>2025</v>
       </c>
@@ -736,7 +754,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>33</v>
       </c>
@@ -744,7 +762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
         <v>34</v>
       </c>
@@ -752,12 +770,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -765,7 +783,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="116" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
@@ -773,12 +791,20 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -796,16 +822,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,7 +845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -833,7 +859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -847,7 +873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -861,17 +887,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5">
+        <v>2037</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>2034</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>4</v>
       </c>
     </row>
@@ -882,10 +922,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -980,7 +1020,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1105,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1230,7 +1270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1355,9 +1395,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <f>MIN(1,MAX(0,(B$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
@@ -1413,35 +1453,35 @@
       </c>
       <c r="O5">
         <f>MIN(1,MAX(0,(O$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f>MIN(1,MAX(0,(P$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <f>MIN(1,MAX(0,(Q$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <f>MIN(1,MAX(0,(R$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>1</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="S5">
         <f>MIN(1,MAX(0,(S$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="T5">
         <f>MIN(1,MAX(0,(T$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U5">
         <f>MIN(1,MAX(0,(U$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="V5">
         <f>MIN(1,MAX(0,(V$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W5">
         <f>MIN(1,MAX(0,(W$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
@@ -1477,6 +1517,131 @@
       </c>
       <c r="AE5">
         <f>MIN(1,MAX(0,(AE$1-VLOOKUP($A5,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A5,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f>MIN(1,MAX(0,(B$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f>MIN(1,MAX(0,(C$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>MIN(1,MAX(0,(D$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>MIN(1,MAX(0,(E$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>MIN(1,MAX(0,(F$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>MIN(1,MAX(0,(G$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>MIN(1,MAX(0,(H$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>MIN(1,MAX(0,(I$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>MIN(1,MAX(0,(J$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>MIN(1,MAX(0,(K$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>MIN(1,MAX(0,(L$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>MIN(1,MAX(0,(M$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>MIN(1,MAX(0,(N$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>MIN(1,MAX(0,(O$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="P6">
+        <f>MIN(1,MAX(0,(P$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q6">
+        <f>MIN(1,MAX(0,(Q$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>0.75</v>
+      </c>
+      <c r="R6">
+        <f>MIN(1,MAX(0,(R$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <f>MIN(1,MAX(0,(S$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <f>MIN(1,MAX(0,(T$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <f>MIN(1,MAX(0,(U$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <f>MIN(1,MAX(0,(V$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <f>MIN(1,MAX(0,(W$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <f>MIN(1,MAX(0,(X$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <f>MIN(1,MAX(0,(Y$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <f>MIN(1,MAX(0,(Z$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <f>MIN(1,MAX(0,(AA$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <f>MIN(1,MAX(0,(AB$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <f>MIN(1,MAX(0,(AC$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <f>MIN(1,MAX(0,(AD$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <f>MIN(1,MAX(0,(AE$1-VLOOKUP($A6,'Gate Parameters'!$A:$D,2,FALSE)+1)/VLOOKUP($A6,'Gate Parameters'!$A:$D,4,FALSE)))</f>
         <v>1</v>
       </c>
     </row>
@@ -1490,10 +1655,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1588,7 +1753,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1713,7 +1878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1838,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1963,9 +2128,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <f>Calc!B5</f>
@@ -2021,35 +2186,35 @@
       </c>
       <c r="O5">
         <f>Calc!O5</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f>Calc!P5</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <f>Calc!Q5</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <f>Calc!R5</f>
-        <v>1</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="S5">
         <f>Calc!S5</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="T5">
         <f>Calc!T5</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U5">
         <f>Calc!U5</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="V5">
         <f>Calc!V5</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W5">
         <f>Calc!W5</f>
@@ -2085,6 +2250,131 @@
       </c>
       <c r="AE5">
         <f>Calc!AE5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f>Calc!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f>Calc!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>Calc!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>Calc!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>Calc!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>Calc!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>Calc!H6</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>Calc!I6</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>Calc!J6</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>Calc!K6</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>Calc!L6</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>Calc!M6</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>Calc!N6</f>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>Calc!O6</f>
+        <v>0.25</v>
+      </c>
+      <c r="P6">
+        <f>Calc!P6</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q6">
+        <f>Calc!Q6</f>
+        <v>0.75</v>
+      </c>
+      <c r="R6">
+        <f>Calc!R6</f>
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <f>Calc!S6</f>
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <f>Calc!T6</f>
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <f>Calc!U6</f>
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <f>Calc!V6</f>
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <f>Calc!W6</f>
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <f>Calc!X6</f>
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <f>Calc!Y6</f>
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <f>Calc!Z6</f>
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <f>Calc!AA6</f>
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <f>Calc!AB6</f>
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <f>Calc!AC6</f>
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <f>Calc!AD6</f>
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <f>Calc!AE6</f>
         <v>1</v>
       </c>
     </row>
